--- a/front-react/public/produits_template.xlsx
+++ b/front-react/public/produits_template.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,35 +429,40 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>uniteId</t>
+          <t>prixAchat</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>unite</t>
+          <t>prixDetail</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>prixAchat</t>
+          <t>prixEnGros</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>prixDetail</t>
+          <t>alerteStock</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>prixEnGros</t>
+          <t>id_unite</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>alerteStock</t>
+          <t>nombreUnitesParConditionnement</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
+        <is>
+          <t>quantiteInitiale</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>magasinIds</t>
         </is>
@@ -475,26 +480,23 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Pièce</t>
-        </is>
+        <v>510</v>
+      </c>
+      <c r="D2" t="n">
+        <v>812</v>
       </c>
       <c r="E2" t="n">
-        <v>510</v>
+        <v>711</v>
       </c>
       <c r="F2" t="n">
-        <v>812</v>
-      </c>
-      <c r="G2" t="n">
-        <v>711</v>
-      </c>
-      <c r="H2" t="n">
         <v>6</v>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>11</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -508,26 +510,23 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Boîte</t>
-        </is>
+        <v>520</v>
+      </c>
+      <c r="D3" t="n">
+        <v>824</v>
       </c>
       <c r="E3" t="n">
-        <v>520</v>
+        <v>722</v>
       </c>
       <c r="F3" t="n">
-        <v>824</v>
-      </c>
-      <c r="G3" t="n">
-        <v>722</v>
-      </c>
-      <c r="H3" t="n">
         <v>7</v>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="n">
+        <v>12</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -541,26 +540,27 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>530</v>
+      </c>
+      <c r="D4" t="n">
+        <v>836</v>
+      </c>
+      <c r="E4" t="n">
+        <v>733</v>
+      </c>
+      <c r="F4" t="n">
+        <v>8</v>
+      </c>
+      <c r="G4" t="n">
         <v>3</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>530</v>
-      </c>
-      <c r="F4" t="n">
-        <v>836</v>
-      </c>
-      <c r="G4" t="n">
-        <v>733</v>
-      </c>
       <c r="H4" t="n">
-        <v>8</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="I4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -574,26 +574,23 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Litre</t>
-        </is>
+        <v>540</v>
+      </c>
+      <c r="D5" t="n">
+        <v>848</v>
       </c>
       <c r="E5" t="n">
-        <v>540</v>
+        <v>744</v>
       </c>
       <c r="F5" t="n">
-        <v>848</v>
-      </c>
-      <c r="G5" t="n">
-        <v>744</v>
-      </c>
-      <c r="H5" t="n">
         <v>9</v>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>14</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -607,26 +604,23 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Pack</t>
-        </is>
+        <v>550</v>
+      </c>
+      <c r="D6" t="n">
+        <v>860</v>
       </c>
       <c r="E6" t="n">
-        <v>550</v>
+        <v>755</v>
       </c>
       <c r="F6" t="n">
-        <v>860</v>
-      </c>
-      <c r="G6" t="n">
-        <v>755</v>
-      </c>
-      <c r="H6" t="n">
         <v>10</v>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>15</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -640,26 +634,27 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>560</v>
+      </c>
+      <c r="D7" t="n">
+        <v>872</v>
+      </c>
+      <c r="E7" t="n">
+        <v>766</v>
+      </c>
+      <c r="F7" t="n">
+        <v>11</v>
+      </c>
+      <c r="G7" t="n">
         <v>6</v>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Mètre</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>560</v>
-      </c>
-      <c r="F7" t="n">
-        <v>872</v>
-      </c>
-      <c r="G7" t="n">
-        <v>766</v>
-      </c>
       <c r="H7" t="n">
-        <v>11</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="I7" t="n">
+        <v>8</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -673,26 +668,23 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Pièce</t>
-        </is>
+        <v>570</v>
+      </c>
+      <c r="D8" t="n">
+        <v>884</v>
       </c>
       <c r="E8" t="n">
-        <v>570</v>
+        <v>777</v>
       </c>
       <c r="F8" t="n">
-        <v>884</v>
-      </c>
-      <c r="G8" t="n">
-        <v>777</v>
-      </c>
-      <c r="H8" t="n">
         <v>12</v>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>17</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -706,26 +698,23 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Boîte</t>
-        </is>
+        <v>580</v>
+      </c>
+      <c r="D9" t="n">
+        <v>896</v>
       </c>
       <c r="E9" t="n">
-        <v>580</v>
+        <v>788</v>
       </c>
       <c r="F9" t="n">
-        <v>896</v>
-      </c>
-      <c r="G9" t="n">
-        <v>788</v>
-      </c>
-      <c r="H9" t="n">
         <v>13</v>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="n">
+        <v>18</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -739,26 +728,27 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>590</v>
+      </c>
+      <c r="D10" t="n">
+        <v>908</v>
+      </c>
+      <c r="E10" t="n">
+        <v>799</v>
+      </c>
+      <c r="F10" t="n">
+        <v>14</v>
+      </c>
+      <c r="G10" t="n">
         <v>3</v>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>590</v>
-      </c>
-      <c r="F10" t="n">
-        <v>908</v>
-      </c>
-      <c r="G10" t="n">
-        <v>799</v>
-      </c>
       <c r="H10" t="n">
-        <v>14</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -772,26 +762,23 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Litre</t>
-        </is>
+        <v>600</v>
+      </c>
+      <c r="D11" t="n">
+        <v>920</v>
       </c>
       <c r="E11" t="n">
-        <v>600</v>
+        <v>810</v>
       </c>
       <c r="F11" t="n">
-        <v>920</v>
-      </c>
-      <c r="G11" t="n">
-        <v>810</v>
-      </c>
-      <c r="H11" t="n">
         <v>5</v>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="n">
+        <v>20</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -805,26 +792,23 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Pack</t>
-        </is>
+        <v>610</v>
+      </c>
+      <c r="D12" t="n">
+        <v>932</v>
       </c>
       <c r="E12" t="n">
-        <v>610</v>
+        <v>821</v>
       </c>
       <c r="F12" t="n">
-        <v>932</v>
-      </c>
-      <c r="G12" t="n">
-        <v>821</v>
-      </c>
-      <c r="H12" t="n">
         <v>6</v>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="n">
+        <v>21</v>
+      </c>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -838,26 +822,27 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>620</v>
+      </c>
+      <c r="D13" t="n">
+        <v>944</v>
+      </c>
+      <c r="E13" t="n">
+        <v>832</v>
+      </c>
+      <c r="F13" t="n">
+        <v>7</v>
+      </c>
+      <c r="G13" t="n">
         <v>6</v>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Mètre</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>620</v>
-      </c>
-      <c r="F13" t="n">
-        <v>944</v>
-      </c>
-      <c r="G13" t="n">
-        <v>832</v>
-      </c>
       <c r="H13" t="n">
-        <v>7</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="I13" t="n">
+        <v>6</v>
+      </c>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -871,26 +856,23 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Pièce</t>
-        </is>
+        <v>630</v>
+      </c>
+      <c r="D14" t="n">
+        <v>956</v>
       </c>
       <c r="E14" t="n">
-        <v>630</v>
+        <v>843</v>
       </c>
       <c r="F14" t="n">
-        <v>956</v>
-      </c>
-      <c r="G14" t="n">
-        <v>843</v>
-      </c>
-      <c r="H14" t="n">
         <v>8</v>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="n">
+        <v>23</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -904,26 +886,23 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Boîte</t>
-        </is>
+        <v>640</v>
+      </c>
+      <c r="D15" t="n">
+        <v>968</v>
       </c>
       <c r="E15" t="n">
-        <v>640</v>
+        <v>854</v>
       </c>
       <c r="F15" t="n">
-        <v>968</v>
-      </c>
-      <c r="G15" t="n">
-        <v>854</v>
-      </c>
-      <c r="H15" t="n">
         <v>9</v>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>24</v>
+      </c>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -937,26 +916,27 @@
         </is>
       </c>
       <c r="C16" t="n">
+        <v>650</v>
+      </c>
+      <c r="D16" t="n">
+        <v>980</v>
+      </c>
+      <c r="E16" t="n">
+        <v>865</v>
+      </c>
+      <c r="F16" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" t="n">
         <v>3</v>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>650</v>
-      </c>
-      <c r="F16" t="n">
-        <v>980</v>
-      </c>
-      <c r="G16" t="n">
-        <v>865</v>
-      </c>
       <c r="H16" t="n">
-        <v>10</v>
-      </c>
-      <c r="I16" t="inlineStr"/>
+        <v>21</v>
+      </c>
+      <c r="I16" t="n">
+        <v>9</v>
+      </c>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -970,26 +950,23 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Litre</t>
-        </is>
+        <v>660</v>
+      </c>
+      <c r="D17" t="n">
+        <v>992</v>
       </c>
       <c r="E17" t="n">
-        <v>660</v>
+        <v>876</v>
       </c>
       <c r="F17" t="n">
-        <v>992</v>
-      </c>
-      <c r="G17" t="n">
-        <v>876</v>
-      </c>
-      <c r="H17" t="n">
         <v>11</v>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="n">
+        <v>26</v>
+      </c>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1003,26 +980,23 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Pack</t>
-        </is>
+        <v>670</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1004</v>
       </c>
       <c r="E18" t="n">
-        <v>670</v>
+        <v>887</v>
       </c>
       <c r="F18" t="n">
-        <v>1004</v>
-      </c>
-      <c r="G18" t="n">
-        <v>887</v>
-      </c>
-      <c r="H18" t="n">
         <v>12</v>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="n">
+        <v>27</v>
+      </c>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1036,26 +1010,27 @@
         </is>
       </c>
       <c r="C19" t="n">
+        <v>680</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1016</v>
+      </c>
+      <c r="E19" t="n">
+        <v>898</v>
+      </c>
+      <c r="F19" t="n">
+        <v>13</v>
+      </c>
+      <c r="G19" t="n">
         <v>6</v>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Mètre</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>680</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1016</v>
-      </c>
-      <c r="G19" t="n">
-        <v>898</v>
-      </c>
       <c r="H19" t="n">
-        <v>13</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4</v>
+      </c>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1069,26 +1044,23 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Pièce</t>
-        </is>
+        <v>690</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1028</v>
       </c>
       <c r="E20" t="n">
-        <v>690</v>
+        <v>909</v>
       </c>
       <c r="F20" t="n">
-        <v>1028</v>
-      </c>
-      <c r="G20" t="n">
-        <v>909</v>
-      </c>
-      <c r="H20" t="n">
         <v>14</v>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="n">
+        <v>29</v>
+      </c>
+      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1102,26 +1074,23 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Boîte</t>
-        </is>
+        <v>700</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1040</v>
       </c>
       <c r="E21" t="n">
-        <v>700</v>
+        <v>920</v>
       </c>
       <c r="F21" t="n">
-        <v>1040</v>
-      </c>
-      <c r="G21" t="n">
-        <v>920</v>
-      </c>
-      <c r="H21" t="n">
         <v>5</v>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="n">
+        <v>10</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1135,26 +1104,27 @@
         </is>
       </c>
       <c r="C22" t="n">
+        <v>710</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1052</v>
+      </c>
+      <c r="E22" t="n">
+        <v>931</v>
+      </c>
+      <c r="F22" t="n">
+        <v>6</v>
+      </c>
+      <c r="G22" t="n">
         <v>3</v>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>710</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1052</v>
-      </c>
-      <c r="G22" t="n">
-        <v>931</v>
-      </c>
       <c r="H22" t="n">
-        <v>6</v>
-      </c>
-      <c r="I22" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="I22" t="n">
+        <v>7</v>
+      </c>
+      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1168,26 +1138,23 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Litre</t>
-        </is>
+        <v>720</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1064</v>
       </c>
       <c r="E23" t="n">
-        <v>720</v>
+        <v>942</v>
       </c>
       <c r="F23" t="n">
-        <v>1064</v>
-      </c>
-      <c r="G23" t="n">
-        <v>942</v>
-      </c>
-      <c r="H23" t="n">
         <v>7</v>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="n">
+        <v>12</v>
+      </c>
+      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1201,26 +1168,23 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Pack</t>
-        </is>
+        <v>730</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1076</v>
       </c>
       <c r="E24" t="n">
-        <v>730</v>
+        <v>953</v>
       </c>
       <c r="F24" t="n">
-        <v>1076</v>
-      </c>
-      <c r="G24" t="n">
-        <v>953</v>
-      </c>
-      <c r="H24" t="n">
         <v>8</v>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="n">
+        <v>13</v>
+      </c>
+      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1234,26 +1198,27 @@
         </is>
       </c>
       <c r="C25" t="n">
+        <v>740</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1088</v>
+      </c>
+      <c r="E25" t="n">
+        <v>964</v>
+      </c>
+      <c r="F25" t="n">
+        <v>9</v>
+      </c>
+      <c r="G25" t="n">
         <v>6</v>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Mètre</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>740</v>
-      </c>
-      <c r="F25" t="n">
-        <v>1088</v>
-      </c>
-      <c r="G25" t="n">
-        <v>964</v>
-      </c>
       <c r="H25" t="n">
-        <v>9</v>
-      </c>
-      <c r="I25" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1267,26 +1232,23 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Pièce</t>
-        </is>
+        <v>750</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1100</v>
       </c>
       <c r="E26" t="n">
-        <v>750</v>
+        <v>975</v>
       </c>
       <c r="F26" t="n">
-        <v>1100</v>
-      </c>
-      <c r="G26" t="n">
-        <v>975</v>
-      </c>
-      <c r="H26" t="n">
         <v>10</v>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="n">
+        <v>15</v>
+      </c>
+      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1300,26 +1262,23 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Boîte</t>
-        </is>
+        <v>760</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1112</v>
       </c>
       <c r="E27" t="n">
-        <v>760</v>
+        <v>986</v>
       </c>
       <c r="F27" t="n">
-        <v>1112</v>
-      </c>
-      <c r="G27" t="n">
-        <v>986</v>
-      </c>
-      <c r="H27" t="n">
         <v>11</v>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="n">
+        <v>16</v>
+      </c>
+      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1333,26 +1292,27 @@
         </is>
       </c>
       <c r="C28" t="n">
+        <v>770</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1124</v>
+      </c>
+      <c r="E28" t="n">
+        <v>997</v>
+      </c>
+      <c r="F28" t="n">
+        <v>12</v>
+      </c>
+      <c r="G28" t="n">
         <v>3</v>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>770</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1124</v>
-      </c>
-      <c r="G28" t="n">
-        <v>997</v>
-      </c>
       <c r="H28" t="n">
-        <v>12</v>
-      </c>
-      <c r="I28" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="I28" t="n">
+        <v>5</v>
+      </c>
+      <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1366,26 +1326,23 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Litre</t>
-        </is>
+        <v>780</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1136</v>
       </c>
       <c r="E29" t="n">
-        <v>780</v>
+        <v>1008</v>
       </c>
       <c r="F29" t="n">
-        <v>1136</v>
-      </c>
-      <c r="G29" t="n">
-        <v>1008</v>
-      </c>
-      <c r="H29" t="n">
         <v>13</v>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="n">
+        <v>18</v>
+      </c>
+      <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1399,26 +1356,23 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Pack</t>
-        </is>
+        <v>790</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1148</v>
       </c>
       <c r="E30" t="n">
-        <v>790</v>
+        <v>1019</v>
       </c>
       <c r="F30" t="n">
-        <v>1148</v>
-      </c>
-      <c r="G30" t="n">
-        <v>1019</v>
-      </c>
-      <c r="H30" t="n">
         <v>14</v>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>19</v>
+      </c>
+      <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1432,26 +1386,27 @@
         </is>
       </c>
       <c r="C31" t="n">
+        <v>800</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1160</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1030</v>
+      </c>
+      <c r="F31" t="n">
+        <v>5</v>
+      </c>
+      <c r="G31" t="n">
         <v>6</v>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Mètre</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>800</v>
-      </c>
-      <c r="F31" t="n">
-        <v>1160</v>
-      </c>
-      <c r="G31" t="n">
-        <v>1030</v>
-      </c>
       <c r="H31" t="n">
-        <v>5</v>
-      </c>
-      <c r="I31" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="I31" t="n">
+        <v>8</v>
+      </c>
+      <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1465,26 +1420,23 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Pièce</t>
-        </is>
+        <v>810</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1172</v>
       </c>
       <c r="E32" t="n">
-        <v>810</v>
+        <v>1041</v>
       </c>
       <c r="F32" t="n">
-        <v>1172</v>
-      </c>
-      <c r="G32" t="n">
-        <v>1041</v>
-      </c>
-      <c r="H32" t="n">
         <v>6</v>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="n">
+        <v>21</v>
+      </c>
+      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1498,26 +1450,23 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Boîte</t>
-        </is>
+        <v>820</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1184</v>
       </c>
       <c r="E33" t="n">
-        <v>820</v>
+        <v>1052</v>
       </c>
       <c r="F33" t="n">
-        <v>1184</v>
-      </c>
-      <c r="G33" t="n">
-        <v>1052</v>
-      </c>
-      <c r="H33" t="n">
         <v>7</v>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="n">
+        <v>22</v>
+      </c>
+      <c r="J33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1531,26 +1480,27 @@
         </is>
       </c>
       <c r="C34" t="n">
+        <v>830</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1196</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1063</v>
+      </c>
+      <c r="F34" t="n">
+        <v>8</v>
+      </c>
+      <c r="G34" t="n">
         <v>3</v>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>830</v>
-      </c>
-      <c r="F34" t="n">
-        <v>1196</v>
-      </c>
-      <c r="G34" t="n">
-        <v>1063</v>
-      </c>
       <c r="H34" t="n">
-        <v>8</v>
-      </c>
-      <c r="I34" t="inlineStr"/>
+        <v>21</v>
+      </c>
+      <c r="I34" t="n">
+        <v>3</v>
+      </c>
+      <c r="J34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1564,26 +1514,23 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Litre</t>
-        </is>
+        <v>840</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1208</v>
       </c>
       <c r="E35" t="n">
-        <v>840</v>
+        <v>1074</v>
       </c>
       <c r="F35" t="n">
-        <v>1208</v>
-      </c>
-      <c r="G35" t="n">
-        <v>1074</v>
-      </c>
-      <c r="H35" t="n">
         <v>9</v>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="n">
+        <v>24</v>
+      </c>
+      <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1597,26 +1544,23 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>5</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Pack</t>
-        </is>
+        <v>850</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1220</v>
       </c>
       <c r="E36" t="n">
-        <v>850</v>
+        <v>1085</v>
       </c>
       <c r="F36" t="n">
-        <v>1220</v>
-      </c>
-      <c r="G36" t="n">
-        <v>1085</v>
-      </c>
-      <c r="H36" t="n">
         <v>10</v>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="n">
+        <v>25</v>
+      </c>
+      <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1630,26 +1574,27 @@
         </is>
       </c>
       <c r="C37" t="n">
+        <v>860</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1232</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1096</v>
+      </c>
+      <c r="F37" t="n">
+        <v>11</v>
+      </c>
+      <c r="G37" t="n">
         <v>6</v>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Mètre</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>860</v>
-      </c>
-      <c r="F37" t="n">
-        <v>1232</v>
-      </c>
-      <c r="G37" t="n">
-        <v>1096</v>
-      </c>
       <c r="H37" t="n">
-        <v>11</v>
-      </c>
-      <c r="I37" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="I37" t="n">
+        <v>6</v>
+      </c>
+      <c r="J37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1663,26 +1608,23 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Pièce</t>
-        </is>
+        <v>870</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1244</v>
       </c>
       <c r="E38" t="n">
-        <v>870</v>
+        <v>1107</v>
       </c>
       <c r="F38" t="n">
-        <v>1244</v>
-      </c>
-      <c r="G38" t="n">
-        <v>1107</v>
-      </c>
-      <c r="H38" t="n">
         <v>12</v>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="n">
+        <v>27</v>
+      </c>
+      <c r="J38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1696,26 +1638,23 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Boîte</t>
-        </is>
+        <v>880</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1256</v>
       </c>
       <c r="E39" t="n">
-        <v>880</v>
+        <v>1118</v>
       </c>
       <c r="F39" t="n">
-        <v>1256</v>
-      </c>
-      <c r="G39" t="n">
-        <v>1118</v>
-      </c>
-      <c r="H39" t="n">
         <v>13</v>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="n">
+        <v>28</v>
+      </c>
+      <c r="J39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1729,26 +1668,27 @@
         </is>
       </c>
       <c r="C40" t="n">
+        <v>890</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1268</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1129</v>
+      </c>
+      <c r="F40" t="n">
+        <v>14</v>
+      </c>
+      <c r="G40" t="n">
         <v>3</v>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>890</v>
-      </c>
-      <c r="F40" t="n">
-        <v>1268</v>
-      </c>
-      <c r="G40" t="n">
-        <v>1129</v>
-      </c>
       <c r="H40" t="n">
-        <v>14</v>
-      </c>
-      <c r="I40" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="I40" t="n">
+        <v>9</v>
+      </c>
+      <c r="J40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1762,26 +1702,23 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Litre</t>
-        </is>
+        <v>900</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1280</v>
       </c>
       <c r="E41" t="n">
-        <v>900</v>
+        <v>1140</v>
       </c>
       <c r="F41" t="n">
-        <v>1280</v>
-      </c>
-      <c r="G41" t="n">
-        <v>1140</v>
-      </c>
-      <c r="H41" t="n">
         <v>5</v>
       </c>
-      <c r="I41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="n">
+        <v>10</v>
+      </c>
+      <c r="J41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1795,26 +1732,23 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Pack</t>
-        </is>
+        <v>910</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1292</v>
       </c>
       <c r="E42" t="n">
-        <v>910</v>
+        <v>1151</v>
       </c>
       <c r="F42" t="n">
-        <v>1292</v>
-      </c>
-      <c r="G42" t="n">
-        <v>1151</v>
-      </c>
-      <c r="H42" t="n">
         <v>6</v>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="n">
+        <v>11</v>
+      </c>
+      <c r="J42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1828,26 +1762,27 @@
         </is>
       </c>
       <c r="C43" t="n">
+        <v>920</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1304</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1162</v>
+      </c>
+      <c r="F43" t="n">
+        <v>7</v>
+      </c>
+      <c r="G43" t="n">
         <v>6</v>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Mètre</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>920</v>
-      </c>
-      <c r="F43" t="n">
-        <v>1304</v>
-      </c>
-      <c r="G43" t="n">
-        <v>1162</v>
-      </c>
       <c r="H43" t="n">
-        <v>7</v>
-      </c>
-      <c r="I43" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="I43" t="n">
+        <v>4</v>
+      </c>
+      <c r="J43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1861,26 +1796,23 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Pièce</t>
-        </is>
+        <v>930</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1316</v>
       </c>
       <c r="E44" t="n">
-        <v>930</v>
+        <v>1173</v>
       </c>
       <c r="F44" t="n">
-        <v>1316</v>
-      </c>
-      <c r="G44" t="n">
-        <v>1173</v>
-      </c>
-      <c r="H44" t="n">
         <v>8</v>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="n">
+        <v>13</v>
+      </c>
+      <c r="J44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1894,26 +1826,23 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Boîte</t>
-        </is>
+        <v>940</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1328</v>
       </c>
       <c r="E45" t="n">
-        <v>940</v>
+        <v>1184</v>
       </c>
       <c r="F45" t="n">
-        <v>1328</v>
-      </c>
-      <c r="G45" t="n">
-        <v>1184</v>
-      </c>
-      <c r="H45" t="n">
         <v>9</v>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="n">
+        <v>14</v>
+      </c>
+      <c r="J45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1927,26 +1856,27 @@
         </is>
       </c>
       <c r="C46" t="n">
+        <v>950</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1340</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1195</v>
+      </c>
+      <c r="F46" t="n">
+        <v>10</v>
+      </c>
+      <c r="G46" t="n">
         <v>3</v>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>950</v>
-      </c>
-      <c r="F46" t="n">
-        <v>1340</v>
-      </c>
-      <c r="G46" t="n">
-        <v>1195</v>
-      </c>
       <c r="H46" t="n">
-        <v>10</v>
-      </c>
-      <c r="I46" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="I46" t="n">
+        <v>7</v>
+      </c>
+      <c r="J46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1960,26 +1890,23 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>4</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Litre</t>
-        </is>
+        <v>960</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1352</v>
       </c>
       <c r="E47" t="n">
-        <v>960</v>
+        <v>1206</v>
       </c>
       <c r="F47" t="n">
-        <v>1352</v>
-      </c>
-      <c r="G47" t="n">
-        <v>1206</v>
-      </c>
-      <c r="H47" t="n">
         <v>11</v>
       </c>
-      <c r="I47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="n">
+        <v>16</v>
+      </c>
+      <c r="J47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1993,26 +1920,23 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>5</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Pack</t>
-        </is>
+        <v>970</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1364</v>
       </c>
       <c r="E48" t="n">
-        <v>970</v>
+        <v>1217</v>
       </c>
       <c r="F48" t="n">
-        <v>1364</v>
-      </c>
-      <c r="G48" t="n">
-        <v>1217</v>
-      </c>
-      <c r="H48" t="n">
         <v>12</v>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="n">
+        <v>17</v>
+      </c>
+      <c r="J48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2026,26 +1950,27 @@
         </is>
       </c>
       <c r="C49" t="n">
+        <v>980</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1376</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1228</v>
+      </c>
+      <c r="F49" t="n">
+        <v>13</v>
+      </c>
+      <c r="G49" t="n">
         <v>6</v>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Mètre</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>980</v>
-      </c>
-      <c r="F49" t="n">
-        <v>1376</v>
-      </c>
-      <c r="G49" t="n">
-        <v>1228</v>
-      </c>
       <c r="H49" t="n">
-        <v>13</v>
-      </c>
-      <c r="I49" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="I49" t="n">
+        <v>2</v>
+      </c>
+      <c r="J49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2059,26 +1984,23 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Pièce</t>
-        </is>
+        <v>990</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1388</v>
       </c>
       <c r="E50" t="n">
-        <v>990</v>
+        <v>1239</v>
       </c>
       <c r="F50" t="n">
-        <v>1388</v>
-      </c>
-      <c r="G50" t="n">
-        <v>1239</v>
-      </c>
-      <c r="H50" t="n">
         <v>14</v>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="n">
+        <v>19</v>
+      </c>
+      <c r="J50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2092,26 +2014,23 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Boîte</t>
-        </is>
+        <v>1000</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1400</v>
       </c>
       <c r="E51" t="n">
-        <v>1000</v>
+        <v>1250</v>
       </c>
       <c r="F51" t="n">
-        <v>1400</v>
-      </c>
-      <c r="G51" t="n">
-        <v>1250</v>
-      </c>
-      <c r="H51" t="n">
         <v>5</v>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="n">
+        <v>20</v>
+      </c>
+      <c r="J51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/front-react/public/produits_template.xlsx
+++ b/front-react/public/produits_template.xlsx
@@ -1,34 +1,52 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="produits" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
   <fonts count="1">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +65,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
@@ -199,6 +150,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -233,6 +185,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -267,20 +220,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -402,227 +351,247 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L5"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>nomProduit</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>prixAchat</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>id_unite</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>nombreUnitesParConditionnement</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>quantiteInitiale</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>productImage</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>caracteristique</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>prixDetail</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>prixEnGros</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>alerteStock</t>
-        </is>
+      <c r="A1" t="str">
+        <v>nomProduit</v>
+      </c>
+      <c r="B1" t="str">
+        <v>prixAchat</v>
+      </c>
+      <c r="C1" t="str">
+        <v>id_unite</v>
+      </c>
+      <c r="D1" t="str">
+        <v>unite_code</v>
+      </c>
+      <c r="E1" t="str">
+        <v>unite_name</v>
+      </c>
+      <c r="F1" t="str">
+        <v>nombreUnitesParConditionnement</v>
+      </c>
+      <c r="G1" t="str">
+        <v>quantiteInitiale</v>
+      </c>
+      <c r="H1" t="str">
+        <v>productImage</v>
+      </c>
+      <c r="I1" t="str">
+        <v>caracteristique</v>
+      </c>
+      <c r="J1" t="str">
+        <v>prixDetail</v>
+      </c>
+      <c r="K1" t="str">
+        <v>prixEnGros</v>
+      </c>
+      <c r="L1" t="str">
+        <v>alerteStock</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Riz Basmati 1kg</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://example.com/riz.jpg</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Riz de qualité supérieure
-Origine Inde</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="A2" t="str">
+        <v>Savon A</v>
+      </c>
+      <c r="B2" t="str">
+        <v>500</v>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v>BOX</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Carton</v>
+      </c>
+      <c r="F2" t="str">
+        <v>12</v>
+      </c>
+      <c r="G2" t="str">
+        <v>5</v>
+      </c>
+      <c r="H2" t="str">
+        <v>https://example.com/savon-a.jpg</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Parfum: citron</v>
+      </c>
+      <c r="J2" t="str">
+        <v>1200</v>
+      </c>
+      <c r="K2" t="str">
+        <v>1000</v>
+      </c>
+      <c r="L2" t="str">
+        <v>10</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Huile d'olive 500ml</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Huile extra vierge
-Première pression</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1500</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="A3" t="str">
+        <v>Brosse B</v>
+      </c>
+      <c r="B3" t="str">
+        <v>150</v>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v>Boîte</v>
+      </c>
+      <c r="F3" t="str">
+        <v>6</v>
+      </c>
+      <c r="G3" t="str">
+        <v>10</v>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>Couleur: rouge</v>
+      </c>
+      <c r="J3" t="str">
+        <v>400</v>
+      </c>
+      <c r="K3" t="str">
+        <v>350</v>
+      </c>
+      <c r="L3" t="str">
+        <v>5</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Sucre blanc 2kg</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>https://example.com/sucre.jpg</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Sucre raffiné
-Sans additifs</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>950</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="A4" t="str">
+        <v>Clou C</v>
+      </c>
+      <c r="B4" t="str">
+        <v>50</v>
+      </c>
+      <c r="C4" t="str">
+        <v>42</v>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v>100</v>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v>80</v>
+      </c>
+      <c r="K4" t="str">
+        <v>60</v>
+      </c>
+      <c r="L4" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Stylo D</v>
+      </c>
+      <c r="B5" t="str">
+        <v>100</v>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v>50</v>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>Encre bleue</v>
+      </c>
+      <c r="J5" t="str">
+        <v>200</v>
+      </c>
+      <c r="K5" t="str">
+        <v>150</v>
+      </c>
+      <c r="L5" t="str">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/front-react/public/produits_template.xlsx
+++ b/front-react/public/produits_template.xlsx
@@ -410,7 +410,7 @@
         <v>id_unite</v>
       </c>
       <c r="D1" t="str">
-        <v>unite_code</v>
+        <v>symbole</v>
       </c>
       <c r="E1" t="str">
         <v>unite_name</v>
@@ -486,7 +486,7 @@
         <v/>
       </c>
       <c r="D3" t="str">
-        <v/>
+        <v>BOÎTE</v>
       </c>
       <c r="E3" t="str">
         <v>Boîte</v>

--- a/front-react/public/produits_template.xlsx
+++ b/front-react/public/produits_template.xlsx
@@ -1,52 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="produits" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="produits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -65,13 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -150,7 +199,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -185,7 +233,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -220,16 +267,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -351,247 +402,374 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>nomProduit</v>
-      </c>
-      <c r="B1" t="str">
-        <v>prixAchat</v>
-      </c>
-      <c r="C1" t="str">
-        <v>id_unite</v>
-      </c>
-      <c r="D1" t="str">
-        <v>symbole</v>
-      </c>
-      <c r="E1" t="str">
-        <v>unite_name</v>
-      </c>
-      <c r="F1" t="str">
-        <v>nombreUnitesParConditionnement</v>
-      </c>
-      <c r="G1" t="str">
-        <v>quantiteInitiale</v>
-      </c>
-      <c r="H1" t="str">
-        <v>productImage</v>
-      </c>
-      <c r="I1" t="str">
-        <v>caracteristique</v>
-      </c>
-      <c r="J1" t="str">
-        <v>prixDetail</v>
-      </c>
-      <c r="K1" t="str">
-        <v>prixEnGros</v>
-      </c>
-      <c r="L1" t="str">
-        <v>alerteStock</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>nomProduit</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>prixAchat</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>prixDetail</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>prixEnGros</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>alerteStock</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>quantiteInitiale</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>emballages</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>productImage</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>caracteristique</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>Savon A</v>
-      </c>
-      <c r="B2" t="str">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Riz 25kg</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Carton:24;Sac:6</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Riz local</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Huile végétale 1L</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>500</v>
       </c>
-      <c r="C2" t="str">
-        <v/>
-      </c>
-      <c r="D2" t="str">
-        <v>BOX</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Carton</v>
-      </c>
-      <c r="F2" t="str">
-        <v>12</v>
-      </c>
-      <c r="G2" t="str">
+      <c r="C3" t="n">
+        <v>700</v>
+      </c>
+      <c r="D3" t="n">
+        <v>600</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Carton:12</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Savon de lessive</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>150</v>
+      </c>
+      <c r="C4" t="n">
+        <v>250</v>
+      </c>
+      <c r="D4" t="n">
+        <v>200</v>
+      </c>
+      <c r="E4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F4" t="n">
         <v>5</v>
       </c>
-      <c r="H2" t="str">
-        <v>https://example.com/savon-a.jpg</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Parfum: citron</v>
-      </c>
-      <c r="J2" t="str">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Carton:48;Paquet:6</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Parfum citron</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Sucre en poudre 1kg</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>400</v>
+      </c>
+      <c r="C5" t="n">
+        <v>600</v>
+      </c>
+      <c r="D5" t="n">
+        <v>500</v>
+      </c>
+      <c r="E5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sac:50</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Lait en poudre 400g</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>1200</v>
       </c>
-      <c r="K2" t="str">
+      <c r="C6" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1400</v>
+      </c>
+      <c r="E6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Carton:24</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Biscuits sucrés</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>180</v>
+      </c>
+      <c r="D7" t="n">
+        <v>150</v>
+      </c>
+      <c r="E7" t="n">
+        <v>20</v>
+      </c>
+      <c r="F7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carton:20;Paquet:5</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Goût vanille</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Boîte d'allumettes</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>25</v>
+      </c>
+      <c r="C8" t="n">
+        <v>50</v>
+      </c>
+      <c r="D8" t="n">
+        <v>40</v>
+      </c>
+      <c r="E8" t="n">
+        <v>30</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Carton:100</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sel fin 1kg</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>200</v>
+      </c>
+      <c r="C9" t="n">
+        <v>350</v>
+      </c>
+      <c r="D9" t="n">
+        <v>300</v>
+      </c>
+      <c r="E9" t="n">
+        <v>15</v>
+      </c>
+      <c r="F9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sac:25</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Thé vert (boîte)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>800</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D10" t="n">
         <v>1000</v>
       </c>
-      <c r="L2" t="str">
+      <c r="E10" t="n">
         <v>10</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Brosse B</v>
-      </c>
-      <c r="B3" t="str">
-        <v>150</v>
-      </c>
-      <c r="C3" t="str">
-        <v/>
-      </c>
-      <c r="D3" t="str">
-        <v>BOÎTE</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Boîte</v>
-      </c>
-      <c r="F3" t="str">
-        <v>6</v>
-      </c>
-      <c r="G3" t="str">
-        <v>10</v>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>Couleur: rouge</v>
-      </c>
-      <c r="J3" t="str">
-        <v>400</v>
-      </c>
-      <c r="K3" t="str">
-        <v>350</v>
-      </c>
-      <c r="L3" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Clou C</v>
-      </c>
-      <c r="B4" t="str">
+      <c r="F10" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carton:12</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>25 sachets par boîte</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Stylo à bille</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
         <v>50</v>
       </c>
-      <c r="C4" t="str">
-        <v>42</v>
-      </c>
-      <c r="D4" t="str">
-        <v/>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
+      <c r="C11" t="n">
         <v>100</v>
       </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v/>
-      </c>
-      <c r="J4" t="str">
-        <v>80</v>
-      </c>
-      <c r="K4" t="str">
-        <v>60</v>
-      </c>
-      <c r="L4" t="str">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Stylo D</v>
-      </c>
-      <c r="B5" t="str">
-        <v>100</v>
-      </c>
-      <c r="C5" t="str">
-        <v/>
-      </c>
-      <c r="D5" t="str">
-        <v/>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
+      <c r="D11" t="n">
+        <v>75</v>
+      </c>
+      <c r="E11" t="n">
+        <v>25</v>
+      </c>
+      <c r="F11" t="n">
         <v>50</v>
       </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>Encre bleue</v>
-      </c>
-      <c r="J5" t="str">
-        <v>200</v>
-      </c>
-      <c r="K5" t="str">
-        <v>150</v>
-      </c>
-      <c r="L5" t="str">
-        <v>5</v>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Bleu, vendu à l'unité</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>